--- a/data.xlsx
+++ b/data.xlsx
@@ -1,91 +1,612 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intel\Documents\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7B0E6F-C752-4AFB-9DB0-A11E62CB5ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2832" yWindow="1548" windowWidth="17280" windowHeight="8832" xr2:uid="{C2043155-F36B-4BD4-866C-DC621EFF66B0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9285"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="nama" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
-  <si>
-    <t>Nama</t>
-  </si>
-  <si>
-    <t>Kelas</t>
-  </si>
-  <si>
-    <t>Hasil</t>
-  </si>
-  <si>
-    <t>Iin</t>
-  </si>
-  <si>
-    <t>Devina</t>
-  </si>
-  <si>
-    <t>Iqbal</t>
-  </si>
-  <si>
-    <t>XI TKJ 1</t>
-  </si>
-  <si>
-    <t>XI AKL 4</t>
-  </si>
-  <si>
-    <t>XI AKL 2</t>
-  </si>
-  <si>
-    <t>XI TKJ 2</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="186">
+  <si>
+    <t>AARON SWAINE VALERIE</t>
+  </si>
+  <si>
+    <t>ADAM SEISA DAMAR ALAM</t>
+  </si>
+  <si>
+    <t>ADELLA PERMATA USMANIA</t>
+  </si>
+  <si>
+    <t>ADINDA NAHDAH LATHIFAH</t>
+  </si>
+  <si>
+    <t>AFWAN MAULANA AZIDAN GHONY</t>
+  </si>
+  <si>
+    <t>AINUN NABILAH SYIFA IYATI</t>
+  </si>
+  <si>
+    <t>AISYAH KIRANI WIJANARKO</t>
+  </si>
+  <si>
+    <t>AISYAH PUTRI IHSANI</t>
+  </si>
+  <si>
+    <t>ALFARIZKY SAFITRAH</t>
+  </si>
+  <si>
+    <t>ALIF VINA AYU LESTARI</t>
+  </si>
+  <si>
+    <t>ALIF ZAIDAN AZMI</t>
+  </si>
+  <si>
+    <t>ALIFYA RATNATHANIA SYAVIRA</t>
+  </si>
+  <si>
+    <t>ALIMAH NAFISA ZARIN</t>
+  </si>
+  <si>
+    <t>ALMIRA FITRI FAUZIYAH</t>
+  </si>
+  <si>
+    <t>ALVINO PUTRA DIKA</t>
+  </si>
+  <si>
+    <t>AMELIA NUR HASANAH</t>
+  </si>
+  <si>
+    <t>AMELLA PUTRI APSALIEN</t>
+  </si>
+  <si>
+    <t>AMIRAH CAHYA RAHMADANI</t>
+  </si>
+  <si>
+    <t>AMIRAH ELVINA ARIFTA</t>
+  </si>
+  <si>
+    <t>ANANDA SEKAR FAHIRA</t>
+  </si>
+  <si>
+    <t>ANDIKA WAHYU MARIONO</t>
+  </si>
+  <si>
+    <t>ANDINI KENDRA PRYATISTA</t>
+  </si>
+  <si>
+    <t>ANGEL WULAN VERONIKA</t>
+  </si>
+  <si>
+    <t>ANISYA FITRIYA RAMADHANI</t>
+  </si>
+  <si>
+    <t>ANJANI KEISHYA AZZAHRA</t>
+  </si>
+  <si>
+    <t>ARASYA ALMUTSIRAH SETYANANTA</t>
+  </si>
+  <si>
+    <t>ARBYAN NAFEBRI DARMAWAN</t>
+  </si>
+  <si>
+    <t>ARDIS MUHAMMAD RAFIF</t>
+  </si>
+  <si>
+    <t>ARYA DHARMAWAN</t>
+  </si>
+  <si>
+    <t>ARYA FEBRIANSYAH WIDJIANTO</t>
+  </si>
+  <si>
+    <t>ATHAYA GADIS XAVIERA</t>
+  </si>
+  <si>
+    <t>AULIA MARDIYANTI</t>
+  </si>
+  <si>
+    <t>AZAM SURYA SAPUTRA</t>
+  </si>
+  <si>
+    <t>AZIZAH FAJRINA KINANTI</t>
+  </si>
+  <si>
+    <t>AZZAM FARRAS PRIATHAMA</t>
+  </si>
+  <si>
+    <t>BAYU BRAMANTYA PRAYOGO</t>
+  </si>
+  <si>
+    <t>BAYU DWI PUTRA UTAMA</t>
+  </si>
+  <si>
+    <t>BELLA QURANISYAH</t>
+  </si>
+  <si>
+    <t>BINTANG PUTRA HARIYONO</t>
+  </si>
+  <si>
+    <t>CANTIKA PUTRI MADANI</t>
+  </si>
+  <si>
+    <t>CARISSA ALMIRA PUTRI</t>
+  </si>
+  <si>
+    <t>CHUSNUL KHAMELIA</t>
+  </si>
+  <si>
+    <t>CHYNTIA AYU SAPUTRI</t>
+  </si>
+  <si>
+    <t>DAHLIA SHERLISA</t>
+  </si>
+  <si>
+    <t>DANIEL CHRISTOPHER SEAN</t>
+  </si>
+  <si>
+    <t>DANEZA TUNGGAL DEWI</t>
+  </si>
+  <si>
+    <t>DARIN DWI OKTA</t>
+  </si>
+  <si>
+    <t>DARA PUSPITA OCTAVIANI</t>
+  </si>
+  <si>
+    <t>DEANA ALMAQHFANY SAFITRI</t>
+  </si>
+  <si>
+    <t>DESYIVA ANGGREINI</t>
+  </si>
+  <si>
+    <t>DEVINDA SAFITRI NURAINI</t>
+  </si>
+  <si>
+    <t>DHEA AULIA</t>
+  </si>
+  <si>
+    <t>DIANA PUTRI NUR ALISYA</t>
+  </si>
+  <si>
+    <t>DIMAS HILMI PUTRA</t>
+  </si>
+  <si>
+    <t>DIMAS PUTRA WIJAYA</t>
+  </si>
+  <si>
+    <t>DIMAS RISKI ADITIA PUTRA</t>
+  </si>
+  <si>
+    <t>DINDA MAULIDYANTI</t>
+  </si>
+  <si>
+    <t>DIWAN BRILLIANT RYSANMAHDI</t>
+  </si>
+  <si>
+    <t>DJIHAN AULIA MAHARANI</t>
+  </si>
+  <si>
+    <t>DWI NURAINI ARDYANTI</t>
+  </si>
+  <si>
+    <t>EDDRIA AMMALIYA</t>
+  </si>
+  <si>
+    <t>EKA FITRIA SARI</t>
+  </si>
+  <si>
+    <t>ELANO FABIO CANAVARO</t>
+  </si>
+  <si>
+    <t>ENZIE PRATAMA MULYA</t>
+  </si>
+  <si>
+    <t>ERSIVI RAMADHANI</t>
+  </si>
+  <si>
+    <t>EVA RIZKY MARDIANTI</t>
+  </si>
+  <si>
+    <t>EVELYN DEVANA PUTRI PRIASETIA</t>
+  </si>
+  <si>
+    <t>EVITA ATIKA PUTRI</t>
+  </si>
+  <si>
+    <t>FAIZA SEPTIANA</t>
+  </si>
+  <si>
+    <t>FAJAR FANY SIDIQ</t>
+  </si>
+  <si>
+    <t>FALIHAH NAILATUS SYARAFAH</t>
+  </si>
+  <si>
+    <t>FARIDATUZZAHIYAH</t>
+  </si>
+  <si>
+    <t>FARIS ADILLAH</t>
+  </si>
+  <si>
+    <t>FEBBY ADITIYA PERMATA DEWI</t>
+  </si>
+  <si>
+    <t>FEBBY AMALIA SYAFIRA</t>
+  </si>
+  <si>
+    <t>FILDZA AL GHAIDZAN</t>
+  </si>
+  <si>
+    <t>FIRSA VANYA HARIZA PUTRI</t>
+  </si>
+  <si>
+    <t>GHONI REAL ABDILLAH</t>
+  </si>
+  <si>
+    <t>HENFIANA CITRA MAHARANI</t>
+  </si>
+  <si>
+    <t>IKA SHABRINA FEBRIYANTI</t>
+  </si>
+  <si>
+    <t>INTAN NUR AINI</t>
+  </si>
+  <si>
+    <t>INTAN OKTA WINDIANA</t>
+  </si>
+  <si>
+    <t>IRA NATHANIA MARVA</t>
+  </si>
+  <si>
+    <t>ISTIANAH MARYANI</t>
+  </si>
+  <si>
+    <t>JASMINE OLIVIA PUTRI</t>
+  </si>
+  <si>
+    <t>JASMINE SETA MAULIDIYAH</t>
+  </si>
+  <si>
+    <t>JELITA OKTAVIANI</t>
+  </si>
+  <si>
+    <t>JESICA AURELIA</t>
+  </si>
+  <si>
+    <t>JOCELYN LAVENZA SANVIOLA</t>
+  </si>
+  <si>
+    <t>JOEVANNI LIONEL ROOSEVELT</t>
+  </si>
+  <si>
+    <t>JOHSUA CRISNATA OKTAVINO</t>
+  </si>
+  <si>
+    <t>KAFKA NAFISHA AREMANITA</t>
+  </si>
+  <si>
+    <t>KANAYA ZIVARA ADISTY</t>
+  </si>
+  <si>
+    <t>KAYRA MARINKA PUTERI</t>
+  </si>
+  <si>
+    <t>KEISHA FORTUNATA ISMUTIYAR</t>
+  </si>
+  <si>
+    <t>KEVIN ADRIANO PUTRA PRADANA</t>
+  </si>
+  <si>
+    <t>KHANZA KAMELA MULYA</t>
+  </si>
+  <si>
+    <t>KHEISYA SALSABILA RAMADHANI</t>
+  </si>
+  <si>
+    <t>KHOLIFATUL RAHMAH</t>
+  </si>
+  <si>
+    <t>KHOIRUN NISA</t>
+  </si>
+  <si>
+    <t>KEYLA ZASKIA NUGRAHA</t>
+  </si>
+  <si>
+    <t>KEYYISA MIR ATU IZZA AR RIDWAN</t>
+  </si>
+  <si>
+    <t>KEYZA RAYYA AZ ZAHRA</t>
+  </si>
+  <si>
+    <t>KEYZHA ANANDA DWI ALIKA</t>
+  </si>
+  <si>
+    <t>LAURA MAYZHE AUDYNA WIJAYA</t>
+  </si>
+  <si>
+    <t>LAILA NUR AFIFA</t>
+  </si>
+  <si>
+    <t>LUTFIA ZAHRA RAHMAWATI</t>
+  </si>
+  <si>
+    <t>LUTFIANA ANDHIKA PUTRI</t>
+  </si>
+  <si>
+    <t>MALVA REVANIA NUR WAHYUNI</t>
+  </si>
+  <si>
+    <t>MARCELLO ALEXANDER VIDIANO</t>
+  </si>
+  <si>
+    <t>MARSHA ARTA FERNANDA</t>
+  </si>
+  <si>
+    <t>MAULANI FEBBY PUTRI WIBISONO</t>
+  </si>
+  <si>
+    <t>MOCH ALFIAN ALIANSYAH</t>
+  </si>
+  <si>
+    <t>MORENO DEDY RADITIA</t>
+  </si>
+  <si>
+    <t>MUNZILAH ARHAM HAFIDZ SYARAHIL</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FATIH ADILLAH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD NAUFAL FERDIANSYAH</t>
+  </si>
+  <si>
+    <t>MUTHIAH RIFDAH KAMILAH</t>
+  </si>
+  <si>
+    <t>NABILA ALIZZY SACHARANI ANINDHEKA</t>
+  </si>
+  <si>
+    <t>NABILA AYU OKTAFIA</t>
+  </si>
+  <si>
+    <t>NABILA YOVIKA NOVITASARI</t>
+  </si>
+  <si>
+    <t>NADIA AISYAH NURRACHMAN</t>
+  </si>
+  <si>
+    <t>NADILA EVITALOKA</t>
+  </si>
+  <si>
+    <t>NAIFA KHANZA RAHMAWATI</t>
+  </si>
+  <si>
+    <t>NAJA SAFA TAZKIA</t>
+  </si>
+  <si>
+    <t>NAILA AULIANSYAH NAVI</t>
+  </si>
+  <si>
+    <t>NAMY AYU DAMAYANTI</t>
+  </si>
+  <si>
+    <t>NANDA AISYAH ARIANTO</t>
+  </si>
+  <si>
+    <t>NATASYA SHITA MAHARANI</t>
+  </si>
+  <si>
+    <t>NATASYA SYAFITRI</t>
+  </si>
+  <si>
+    <t>NOVALINA MADINATUZZAHRAH</t>
+  </si>
+  <si>
+    <t>NUR HIDAYAH</t>
+  </si>
+  <si>
+    <t>OKTAVIA FITRIYANI</t>
+  </si>
+  <si>
+    <t>OKTAVIA NUR AZIIZAH</t>
+  </si>
+  <si>
+    <t>PASCALINE FAJAR RACHMAWATI ANDINI</t>
+  </si>
+  <si>
+    <t>PUTRI ARIA MANDELA</t>
+  </si>
+  <si>
+    <t>PUTRI AULIA SAFITRI</t>
+  </si>
+  <si>
+    <t>PUTRI BALQIS KHOIRUNISA</t>
+  </si>
+  <si>
+    <t>PUTRIANI KRISMA CHOIRUNISA</t>
+  </si>
+  <si>
+    <t>RAFA AKILA RASKY</t>
+  </si>
+  <si>
+    <t>RADITYA RAMANIYA ZAHRAN WINARKO</t>
+  </si>
+  <si>
+    <t>RAJI FIKRI AULIA</t>
+  </si>
+  <si>
+    <t>RAGNALA NAURA PUTERI</t>
+  </si>
+  <si>
+    <t>RENDYCA IQBAL WARDHANA</t>
+  </si>
+  <si>
+    <t>REVAYA HELWA THALIB</t>
+  </si>
+  <si>
+    <t>REYHAN ATHALLAH ARYA SENA</t>
+  </si>
+  <si>
+    <t>SAFIRA KHAIRUNISA</t>
+  </si>
+  <si>
+    <t>SAFA AYU MAHARANI</t>
+  </si>
+  <si>
+    <t>SAFA PUTRI ARI ANDRI</t>
+  </si>
+  <si>
+    <t>SALSABILA OLIVIA</t>
+  </si>
+  <si>
+    <t>SALSABILA PRADITA EKA PUTRI</t>
+  </si>
+  <si>
+    <t>SALWA AULIYA EFENDI</t>
+  </si>
+  <si>
+    <t>SATRIA YUDHISTIRA</t>
+  </si>
+  <si>
+    <t>SAVA ANINDITA</t>
+  </si>
+  <si>
+    <t>SHABRINA AURA SYAFAILLAH</t>
+  </si>
+  <si>
+    <t>SHAFA SISVIRTA SARI</t>
+  </si>
+  <si>
+    <t>SHAFURA SHALIHAN NISA</t>
+  </si>
+  <si>
+    <t>SHEILA RAHMANIA ARYANTI</t>
+  </si>
+  <si>
+    <t>SHELIN SONIA PUTRI</t>
+  </si>
+  <si>
+    <t>SHOBIRIN NURIL ANWAR</t>
+  </si>
+  <si>
+    <t>SONIA ZASKYA ZIVA</t>
+  </si>
+  <si>
+    <t>SYAFIRA AZZAHRA</t>
+  </si>
+  <si>
+    <t>TANTRI NUR AINI PUTRI</t>
+  </si>
+  <si>
+    <t>TANZILUR ROHMA</t>
+  </si>
+  <si>
+    <t>TASYA AYUNDA RAMADHANI</t>
+  </si>
+  <si>
+    <t>THALITA NUR FAUZIAH</t>
+  </si>
+  <si>
+    <t>TRI INTAN NURAINI</t>
+  </si>
+  <si>
+    <t>VANNO VERISCO</t>
+  </si>
+  <si>
+    <t>VANIYA SALSABILA</t>
+  </si>
+  <si>
+    <t>YOVIE EMERALDY ADAM PRAYOGA</t>
+  </si>
+  <si>
+    <t>YUSTINA MARIA RAMBU GOLAR</t>
+  </si>
+  <si>
+    <t>YUZI NOVI ABSARI</t>
+  </si>
+  <si>
+    <t>ZAKIY SARIY ABDI AMRULLAH</t>
+  </si>
+  <si>
+    <t>ZASKIA PUTRI AISYAH</t>
+  </si>
+  <si>
+    <t>ZILVANA REIBA AULIA RAZAQ</t>
+  </si>
+  <si>
+    <t>NAMA</t>
+  </si>
+  <si>
+    <t>HASIL</t>
   </si>
   <si>
     <t>Lulus</t>
   </si>
   <si>
-    <t>Tidak Lulus</t>
-  </si>
-  <si>
-    <t>FARREL</t>
+    <t>Tidak lulus</t>
+  </si>
+  <si>
+    <t>PUTRI SAKINA AVRILLANINGSIH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAHAYA MUTIARA </t>
+  </si>
+  <si>
+    <t>LAILATUL FITRI</t>
+  </si>
+  <si>
+    <t>CAMELIA RISTA AZZARAH</t>
+  </si>
+  <si>
+    <t>INTAN OKTAVIYANI PUTRI</t>
+  </si>
+  <si>
+    <t>CALLISTA ABDIA AVELINTORO</t>
+  </si>
+  <si>
+    <t>REVANIA MUFIDAH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,10 +650,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -167,7 +699,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -179,7 +711,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -196,9 +728,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -226,31 +758,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -278,23 +793,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -446,69 +944,1511 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2913C84B-2987-423C-A225-69F8E4228AEE}">
-  <dimension ref="A2:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F184"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIF($B$3:$B$184,D3)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4">
+        <f>COUNTIF($B$3:$B$184,D4)</f>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
+      <c r="B15" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A3:A177">
+    <sortCondition ref="A3"/>
+  </sortState>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B184">
+      <formula1>$D$3:$D$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417629DA-E103-4EBC-A060-620B54DC8358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8732C6EB-A611-4056-868A-059AE0030A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nama" sheetId="1" r:id="rId1"/>
+    <sheet name="Lembar1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nama!$A$1:$B$2</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="189">
   <si>
     <t>AARON SWAINE VALERIE</t>
   </si>
@@ -561,6 +565,9 @@
     <t>ZILVANA REIBA AULIA RAZAQ</t>
   </si>
   <si>
+    <t>NAMA</t>
+  </si>
+  <si>
     <t>Lulus</t>
   </si>
   <si>
@@ -586,6 +593,12 @@
   </si>
   <si>
     <t>REVANIA MUFIDAH</t>
+  </si>
+  <si>
+    <t>CALLISTA ALODIA</t>
+  </si>
+  <si>
+    <t>SHAN NAFTALY</t>
   </si>
   <si>
     <t>Nama</t>
@@ -633,7 +646,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -656,11 +669,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -671,6 +699,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B184"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.33203125" bestFit="1" customWidth="1"/>
@@ -963,16 +994,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>185</v>
+      <c r="A1" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -987,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -995,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1003,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1019,7 +1050,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1027,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1035,7 +1066,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1043,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1051,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1067,7 +1098,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1075,7 +1106,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1083,7 +1114,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1091,7 +1122,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1099,7 +1130,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1107,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1115,7 +1146,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1123,7 +1154,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1131,7 +1162,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1147,7 +1178,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -1155,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1163,7 +1194,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -1171,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1179,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -1187,7 +1218,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1219,7 +1250,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1227,7 +1258,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1235,7 +1266,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1243,7 +1274,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1251,7 +1282,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1267,7 +1298,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1275,7 +1306,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1283,7 +1314,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1291,7 +1322,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1299,7 +1330,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1307,7 +1338,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1315,7 +1346,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1323,7 +1354,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -1331,7 +1362,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1339,7 +1370,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1347,7 +1378,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1355,7 +1386,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1363,7 +1394,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1371,7 +1402,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1379,7 +1410,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1387,7 +1418,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1395,7 +1426,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1403,7 +1434,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1419,7 +1450,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1427,7 +1458,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1435,7 +1466,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1443,7 +1474,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -1451,7 +1482,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1459,7 +1490,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1467,7 +1498,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1475,7 +1506,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1483,7 +1514,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1491,7 +1522,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1499,7 +1530,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -1507,7 +1538,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -1515,7 +1546,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -1523,7 +1554,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -1531,7 +1562,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1539,7 +1570,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1547,7 +1578,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -1555,7 +1586,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1563,7 +1594,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1571,7 +1602,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1579,7 +1610,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1587,7 +1618,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -1603,7 +1634,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -1611,7 +1642,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1619,7 +1650,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1627,7 +1658,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1635,7 +1666,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1643,7 +1674,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1651,7 +1682,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1659,7 +1690,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -1667,7 +1698,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -1675,7 +1706,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1683,7 +1714,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -1691,7 +1722,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1699,7 +1730,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1707,7 +1738,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1715,7 +1746,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -1723,7 +1754,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -1731,7 +1762,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -1739,7 +1770,7 @@
         <v>95</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -1747,7 +1778,7 @@
         <v>100</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -1755,7 +1786,7 @@
         <v>101</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -1763,7 +1794,7 @@
         <v>102</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -1771,7 +1802,7 @@
         <v>103</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -1779,7 +1810,7 @@
         <v>96</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -1787,7 +1818,7 @@
         <v>97</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -1795,7 +1826,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -1803,7 +1834,7 @@
         <v>98</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -1811,7 +1842,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
@@ -1819,7 +1850,7 @@
         <v>104</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -1827,7 +1858,7 @@
         <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -1835,7 +1866,7 @@
         <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
@@ -1843,7 +1874,7 @@
         <v>108</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1851,7 +1882,7 @@
         <v>109</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -1859,7 +1890,7 @@
         <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
@@ -1867,7 +1898,7 @@
         <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -1883,7 +1914,7 @@
         <v>113</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
@@ -1891,7 +1922,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
@@ -1899,7 +1930,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
@@ -1907,7 +1938,7 @@
         <v>114</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -1915,7 +1946,7 @@
         <v>117</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
@@ -1923,7 +1954,7 @@
         <v>118</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -1931,7 +1962,7 @@
         <v>119</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -1939,7 +1970,7 @@
         <v>120</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -1947,7 +1978,7 @@
         <v>121</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
@@ -1955,7 +1986,7 @@
         <v>122</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -1963,7 +1994,7 @@
         <v>123</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -1971,7 +2002,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
@@ -1979,7 +2010,7 @@
         <v>124</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
@@ -1987,7 +2018,7 @@
         <v>126</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
@@ -1995,7 +2026,7 @@
         <v>127</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
@@ -2003,7 +2034,7 @@
         <v>128</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
@@ -2011,7 +2042,7 @@
         <v>129</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
@@ -2019,7 +2050,7 @@
         <v>130</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
@@ -2027,7 +2058,7 @@
         <v>131</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -2035,7 +2066,7 @@
         <v>132</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
@@ -2043,7 +2074,7 @@
         <v>133</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -2051,7 +2082,7 @@
         <v>134</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
@@ -2059,7 +2090,7 @@
         <v>135</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
@@ -2067,7 +2098,7 @@
         <v>136</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
@@ -2075,7 +2106,7 @@
         <v>137</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
@@ -2083,7 +2114,7 @@
         <v>138</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
@@ -2091,7 +2122,7 @@
         <v>140</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
@@ -2099,7 +2130,7 @@
         <v>139</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
@@ -2107,7 +2138,7 @@
         <v>142</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -2115,7 +2146,7 @@
         <v>141</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -2123,7 +2154,7 @@
         <v>143</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
@@ -2131,7 +2162,7 @@
         <v>144</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -2139,7 +2170,7 @@
         <v>145</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -2147,7 +2178,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -2155,7 +2186,7 @@
         <v>148</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
@@ -2163,7 +2194,7 @@
         <v>146</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -2171,7 +2202,7 @@
         <v>149</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
@@ -2179,7 +2210,7 @@
         <v>150</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -2187,7 +2218,7 @@
         <v>151</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -2195,7 +2226,7 @@
         <v>152</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -2203,7 +2234,7 @@
         <v>153</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -2211,7 +2242,7 @@
         <v>154</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
@@ -2219,7 +2250,7 @@
         <v>155</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
@@ -2227,7 +2258,7 @@
         <v>156</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
@@ -2235,7 +2266,7 @@
         <v>157</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
@@ -2243,7 +2274,7 @@
         <v>158</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -2251,7 +2282,7 @@
         <v>159</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -2259,7 +2290,7 @@
         <v>160</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
@@ -2267,7 +2298,7 @@
         <v>161</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
@@ -2275,7 +2306,7 @@
         <v>162</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
@@ -2283,7 +2314,7 @@
         <v>163</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -2291,7 +2322,7 @@
         <v>164</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -2299,7 +2330,7 @@
         <v>165</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
@@ -2307,7 +2338,7 @@
         <v>166</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -2315,7 +2346,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
@@ -2323,7 +2354,7 @@
         <v>167</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
@@ -2331,7 +2362,7 @@
         <v>169</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -2339,7 +2370,7 @@
         <v>170</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
@@ -2347,7 +2378,7 @@
         <v>171</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -2355,7 +2386,7 @@
         <v>172</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -2363,7 +2394,7 @@
         <v>173</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -2371,66 +2402,83 @@
         <v>174</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B186" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A177">
     <sortCondition ref="A3"/>
   </sortState>
@@ -2440,11 +2488,334 @@
     <mergeCell ref="B1:B2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B184" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B186" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$D$3:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAEC2F6-21F6-FD43-94FB-DA3E7C014C0B}">
+  <dimension ref="A1:A62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="43.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8732C6EB-A611-4056-868A-059AE0030A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4DB717-E95F-4CFE-8864-5FE7D828AF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="190">
   <si>
     <t>AARON SWAINE VALERIE</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>Hasil</t>
+  </si>
+  <si>
+    <t>ANJANI PUTRI LINGKORO</t>
   </si>
 </sst>
 </file>
@@ -688,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -706,6 +709,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B186"/>
+  <dimension ref="A1:B187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.33203125" bestFit="1" customWidth="1"/>
@@ -2474,6 +2478,14 @@
         <v>186</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2488,12 +2500,12 @@
     <mergeCell ref="B1:B2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B186" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B187" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$D$3:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4DB717-E95F-4CFE-8864-5FE7D828AF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC9DB79-37E9-4BF5-8DAD-DB8F33E7493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="191">
   <si>
     <t>AARON SWAINE VALERIE</t>
   </si>
@@ -608,6 +608,9 @@
   </si>
   <si>
     <t>ANJANI PUTRI LINGKORO</t>
+  </si>
+  <si>
+    <t>IBNATY NAURAH SALSABILA</t>
   </si>
 </sst>
 </file>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B187"/>
+  <dimension ref="A1:B188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.33203125" bestFit="1" customWidth="1"/>
@@ -2486,6 +2489,14 @@
         <v>189</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2500,7 +2511,7 @@
     <mergeCell ref="B1:B2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B187" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B188" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$D$3:$D$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC9DB79-37E9-4BF5-8DAD-DB8F33E7493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D34B277-AC6E-4153-9C24-2CA0D06EF83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="192">
   <si>
     <t>AARON SWAINE VALERIE</t>
   </si>
@@ -611,6 +611,9 @@
   </si>
   <si>
     <t>IBNATY NAURAH SALSABILA</t>
+  </si>
+  <si>
+    <t>CAHAYA MUTIARA</t>
   </si>
 </sst>
 </file>
@@ -2422,7 +2425,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>176</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USer\Documents\VSC\Pengumuman koperasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D34B277-AC6E-4153-9C24-2CA0D06EF83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D33C509-5A89-47CF-A57E-B11B653E3906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
